--- a/testdata/dirty-retail/sales.xlsx
+++ b/testdata/dirty-retail/sales.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Quarterly Sales Report</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>0001</t>
+  </si>
+  <si>
+    <t>LATAM</t>
+  </si>
+  <si>
+    <t>Latin America</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -556,6 +562,14 @@
         <v>23</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
